--- a/ig/DM-SIDOBA/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-JDV-J34-CategorieOrganisation-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="637">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -216,7 +216,7 @@
     <t>20</t>
   </si>
   <si>
-    <t>Unité d'urgences polyvalentes</t>
+    <t>Structure des urgences polyvalentes 24h/24 7j/7</t>
   </si>
   <si>
     <t>21</t>
@@ -948,7 +948,7 @@
     <t>146</t>
   </si>
   <si>
-    <t>Unité de prise en charge des brûlés</t>
+    <t>Unité hospitalière de brûlologie</t>
   </si>
   <si>
     <t>148</t>
@@ -1873,6 +1873,48 @@
   </si>
   <si>
     <t>Cabinet de ville infirmier en pratique avancée en santé mentale</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Unité d’Education Thérapeutique du Patient (ETP)</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Unité de réanimation des brûlés</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Unité Sanitaire en Milieu Pénitentiaire (USMP, ex UCSA)</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Structure des urgences pédiatriques</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Pharmacie d'officine (dont mutualiste)</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Antennes des urgences</t>
   </si>
   <si>
     <t/>
@@ -2143,7 +2185,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B299"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4531,15 +4573,71 @@
         <v>620</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B300" t="s" s="2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B301" t="s" s="2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B302" t="s" s="2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B303" t="s" s="2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B304" t="s" s="2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B305" t="s" s="2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>636</v>
       </c>
     </row>
   </sheetData>
